--- a/output/2026-09-13_22_Croazia_Primorsko-goranska_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-09-13_22_Croazia_Primorsko-goranska_Componentistica_Ventilazione_industriale.xlsx
@@ -474,7 +474,6 @@
           <t>K. Arsen d.o.o.</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Rijeka (Škurinje), Primorsko-goranska</t>
@@ -658,10 +657,9 @@
           <t>051 818 626 / 098 459 186</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Produttore di componenti per ventilazione industriale e depolverazione (ventilatori di trasporto, filtri, silos, cicloni, cabine insonorizzate), attiva dal 1995. Email non reperibile da fonte verificabile, lasciata vuota.</t>
+          <t>Produttore di componenti per ventilazione industriale e depolverazione (ventilatori di trasporto, filtri, silos, cicloni, cabine insonorizzate), attiva dal 1995. Email non reperibile da fonte verificabile, lasciata vuota. [DUPLICATO — vedi anche: 2026-09-12_23_Croazia_Varazdinska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">

--- a/output/2026-09-13_22_Croazia_Primorsko-goranska_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-09-13_22_Croazia_Primorsko-goranska_Componentistica_Ventilazione_industriale.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
